--- a/QCM6_SVT.xlsx
+++ b/QCM6_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D336DCCF-6461-4C0B-9349-86D5002F56F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845ADE8C-18F1-4DBE-96CE-CA8D68EC60C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,9 +57,6 @@
     <t>Explication</t>
   </si>
   <si>
-    <t>QCM Chapitre 5</t>
-  </si>
-  <si>
     <t>Selon la loi de H-W, la stabilité des fréquences des deux allèles d'un caractère héréditaire, dans une population naturelle, implique que :</t>
   </si>
   <si>
@@ -346,6 +343,9 @@
   </si>
   <si>
     <t>La mutation représentée &lt;img src="/images/SVT_QCM6_Q11.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est une mutation:</t>
+  </si>
+  <si>
+    <t>QCM Chapitre 6</t>
   </si>
 </sst>
 </file>
@@ -786,522 +786,522 @@
     </row>
     <row r="2" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="H3" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="H5" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="H6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="H7" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="H8" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="H9" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="H10" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="H12" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="H14" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="H15" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="H16" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="H17" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="H18" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="H19" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="H20" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="H21" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/QCM6_SVT.xlsx
+++ b/QCM6_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845ADE8C-18F1-4DBE-96CE-CA8D68EC60C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82A85DB-6B4A-4264-AF63-2E829D3D6E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -342,10 +342,10 @@
     <t>De femmes hémophiles est de 0,1</t>
   </si>
   <si>
-    <t>La mutation représentée &lt;img src="/images/SVT_QCM6_Q11.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est une mutation:</t>
-  </si>
-  <si>
     <t>QCM Chapitre 6</t>
+  </si>
+  <si>
+    <t>La mutation représentée &lt;img src="/images/SVT_QCM6_Q13.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est une mutation:</t>
   </si>
 </sst>
 </file>
@@ -786,7 +786,7 @@
     </row>
     <row r="2" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>10</v>
@@ -812,7 +812,7 @@
     </row>
     <row r="3" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>11</v>
@@ -838,7 +838,7 @@
     </row>
     <row r="4" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>12</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="5" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>13</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="6" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>14</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="7" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>15</v>
@@ -942,7 +942,7 @@
     </row>
     <row r="8" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>16</v>
@@ -968,7 +968,7 @@
     </row>
     <row r="9" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="10" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>18</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="11" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>19</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="12" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>20</v>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="13" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>21</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="14" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="15" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>22</v>
@@ -1150,7 +1150,7 @@
     </row>
     <row r="16" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>23</v>
@@ -1176,7 +1176,7 @@
     </row>
     <row r="17" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>24</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="18" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>25</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="19" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>26</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="20" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>27</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="21" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>28</v>

--- a/QCM6_SVT.xlsx
+++ b/QCM6_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82A85DB-6B4A-4264-AF63-2E829D3D6E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108E9691-28CB-4D08-A4DE-3B58CAE856ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="109">
   <si>
     <t>Question</t>
   </si>
@@ -346,6 +346,12 @@
   </si>
   <si>
     <t>La mutation représentée &lt;img src="/images/SVT_QCM6_Q13.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est une mutation:</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>SVT_QCM6_Q13.png</t>
   </si>
 </sst>
 </file>
@@ -428,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -440,6 +446,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -744,18 +753,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="30.42578125" customWidth="1"/>
     <col min="4" max="7" width="35" customWidth="1"/>
-    <col min="8" max="8" width="33.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="8" max="9" width="33.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -781,10 +790,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>105</v>
       </c>
@@ -809,8 +821,9 @@
       <c r="H2" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>105</v>
       </c>
@@ -835,8 +848,9 @@
       <c r="H3" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>105</v>
       </c>
@@ -861,8 +875,9 @@
       <c r="H4" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>105</v>
       </c>
@@ -887,8 +902,9 @@
       <c r="H5" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>105</v>
       </c>
@@ -913,8 +929,9 @@
       <c r="H6" s="4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>105</v>
       </c>
@@ -939,8 +956,9 @@
       <c r="H7" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>105</v>
       </c>
@@ -965,8 +983,9 @@
       <c r="H8" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>105</v>
       </c>
@@ -991,8 +1010,9 @@
       <c r="H9" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>105</v>
       </c>
@@ -1017,8 +1037,9 @@
       <c r="H10" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>105</v>
       </c>
@@ -1043,8 +1064,9 @@
       <c r="H11" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>105</v>
       </c>
@@ -1069,8 +1091,9 @@
       <c r="H12" s="4" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>105</v>
       </c>
@@ -1095,8 +1118,9 @@
       <c r="H13" s="4" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>105</v>
       </c>
@@ -1121,8 +1145,11 @@
       <c r="H14" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>105</v>
       </c>
@@ -1147,8 +1174,9 @@
       <c r="H15" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>105</v>
       </c>
@@ -1173,8 +1201,9 @@
       <c r="H16" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>105</v>
       </c>
@@ -1199,8 +1228,9 @@
       <c r="H17" s="4" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>105</v>
       </c>
@@ -1225,8 +1255,9 @@
       <c r="H18" s="4" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>105</v>
       </c>
@@ -1251,8 +1282,9 @@
       <c r="H19" s="4" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>105</v>
       </c>
@@ -1277,8 +1309,9 @@
       <c r="H20" s="4" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>105</v>
       </c>
@@ -1303,6 +1336,7 @@
       <c r="H21" s="4" t="s">
         <v>102</v>
       </c>
+      <c r="I21" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/QCM6_SVT.xlsx
+++ b/QCM6_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108E9691-28CB-4D08-A4DE-3B58CAE856ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94374E69-58D2-4C00-B767-8640B46CAE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -342,9 +342,6 @@
     <t>De femmes hémophiles est de 0,1</t>
   </si>
   <si>
-    <t>QCM Chapitre 6</t>
-  </si>
-  <si>
     <t>La mutation représentée &lt;img src="/images/SVT_QCM6_Q13.png" alt="A"class="h-20 block ml-auto my-1" /&gt; est une mutation:</t>
   </si>
   <si>
@@ -352,6 +349,9 @@
   </si>
   <si>
     <t>SVT_QCM6_Q13.png</t>
+  </si>
+  <si>
+    <t>TEST : La génétique des populations</t>
   </si>
 </sst>
 </file>
@@ -790,15 +790,15 @@
         <v>8</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>10</v>
@@ -823,9 +823,9 @@
       </c>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>11</v>
@@ -850,9 +850,9 @@
       </c>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>12</v>
@@ -877,9 +877,9 @@
       </c>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>13</v>
@@ -904,9 +904,9 @@
       </c>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>14</v>
@@ -931,9 +931,9 @@
       </c>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>15</v>
@@ -958,9 +958,9 @@
       </c>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>16</v>
@@ -985,9 +985,9 @@
       </c>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -1012,9 +1012,9 @@
       </c>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>18</v>
@@ -1039,9 +1039,9 @@
       </c>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>19</v>
@@ -1066,9 +1066,9 @@
       </c>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>20</v>
@@ -1093,9 +1093,9 @@
       </c>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>21</v>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="I13" s="5"/>
     </row>
-    <row r="14" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -1146,12 +1146,12 @@
         <v>78</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>22</v>
@@ -1176,9 +1176,9 @@
       </c>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>23</v>
@@ -1203,9 +1203,9 @@
       </c>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>24</v>
@@ -1230,9 +1230,9 @@
       </c>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>25</v>
@@ -1257,9 +1257,9 @@
       </c>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>26</v>
@@ -1284,9 +1284,9 @@
       </c>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>27</v>
@@ -1311,9 +1311,9 @@
       </c>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>28</v>
